--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260630.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260630.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D95"/>
+  <dimension ref="A1:D96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -909,17 +909,17 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>5,248,520</t>
+          <t>180,515</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -931,17 +931,17 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>1,325,000</t>
+          <t>5,248,520</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -953,17 +953,17 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>180,515</t>
+          <t>1,325,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -1767,17 +1767,17 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>288,000</t>
+          <t>92,000</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -1789,17 +1789,17 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>797,000</t>
+          <t>288,000</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -1811,17 +1811,17 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>4,914,956</t>
+          <t>797,000</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -1833,17 +1833,17 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>92,000</t>
+          <t>4,914,956</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -1943,17 +1943,17 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>155,000</t>
+          <t>176,000</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -1965,17 +1965,17 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>994,121</t>
+          <t>155,000</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -1987,17 +1987,17 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>鴻準</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>1,741,000</t>
+          <t>994,121</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -2009,17 +2009,17 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>鴻準</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>169,000</t>
+          <t>1,741,000</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -2031,17 +2031,17 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>64,538</t>
+          <t>169,000</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -2053,17 +2053,17 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>176,000</t>
+          <t>64,538</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -2239,6 +2239,24 @@
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>RDI_NTD</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>-248,403,414</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
